--- a/empirical_study/codebook.xlsx
+++ b/empirical_study/codebook.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="84">
   <si>
     <t>Code for Symptoms</t>
   </si>
@@ -49,16 +49,10 @@
     <t>This category covers performance problems with a long kernel launch or execution time.</t>
   </si>
   <si>
-    <t>Long Execution Time for Kernel Function</t>
-  </si>
-  <si>
-    <t>The performance problems manifest a long execution time for the kernel function.</t>
-  </si>
-  <si>
-    <t>Long Execution Time for Code Blocks</t>
-  </si>
-  <si>
-    <t>The performance problems manifest a long execution time for specific code blocks.</t>
+    <t>Long Kernel Execution Time</t>
+  </si>
+  <si>
+    <t>The performance problems manifest a long execution time.</t>
   </si>
   <si>
     <t>Long Kernel Launch Time</t>
@@ -1252,7 +1246,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="30.2727272727273" customWidth="1"/>
@@ -1306,19 +1300,19 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2" t="s">
+      <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
         <v>13</v>
       </c>
@@ -1333,19 +1327,19 @@
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2" t="s">
+      <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
+      <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="2"/>
       <c r="C10" s="2" t="s">
         <v>19</v>
       </c>
@@ -1369,58 +1363,58 @@
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="2"/>
+      <c r="A13" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="B13" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>28</v>
-      </c>
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="2"/>
+    <row r="16" ht="15" spans="1:3">
+      <c r="A16" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" ht="15" spans="1:3">
-      <c r="A17" s="1" t="s">
+    <row r="17" spans="1:3">
+      <c r="A17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2"/>
       <c r="C19" s="2" t="s">
         <v>30</v>
       </c>
@@ -1471,19 +1465,19 @@
       </c>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2" t="s">
+      <c r="A25" s="2" t="s">
         <v>41</v>
       </c>
+      <c r="B25" s="2"/>
       <c r="C25" s="2" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B26" s="2"/>
       <c r="C26" s="2" t="s">
         <v>44</v>
       </c>
@@ -1525,24 +1519,24 @@
       </c>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2" t="s">
+      <c r="A31" s="2" t="s">
         <v>53</v>
       </c>
+      <c r="B31" s="2"/>
       <c r="C31" s="2" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B32" s="2"/>
       <c r="C32" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:8">
       <c r="A33" s="2"/>
       <c r="B33" s="2" t="s">
         <v>57</v>
@@ -1550,12 +1544,17 @@
       <c r="C33" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2" t="s">
+      <c r="A34" s="2" t="s">
         <v>59</v>
       </c>
+      <c r="B34" s="2"/>
       <c r="C34" s="2" t="s">
         <v>60</v>
       </c>
@@ -1566,10 +1565,10 @@
       <c r="H34" s="2"/>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B35" s="2"/>
       <c r="C35" s="2" t="s">
         <v>62</v>
       </c>
@@ -1594,10 +1593,10 @@
       <c r="H36" s="2"/>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="2"/>
-      <c r="B37" s="2" t="s">
+      <c r="A37" s="2" t="s">
         <v>65</v>
       </c>
+      <c r="B37" s="2"/>
       <c r="C37" s="2" t="s">
         <v>66</v>
       </c>
@@ -1608,10 +1607,10 @@
       <c r="H37" s="2"/>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="2" t="s">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B38" s="2"/>
       <c r="C38" s="2" t="s">
         <v>68</v>
       </c>
@@ -1636,12 +1635,14 @@
       <c r="H39" s="2"/>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="2"/>
+      <c r="A40" s="2" t="s">
+        <v>71</v>
+      </c>
       <c r="B40" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
@@ -1651,11 +1652,9 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B41" s="2" t="s">
         <v>74</v>
       </c>
+      <c r="B41" s="2"/>
       <c r="C41" s="2" t="s">
         <v>75</v>
       </c>
@@ -1666,10 +1665,10 @@
       <c r="H41" s="2"/>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="2" t="s">
+      <c r="A42" s="2"/>
+      <c r="B42" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B42" s="2"/>
       <c r="C42" s="2" t="s">
         <v>77</v>
       </c>
@@ -1707,41 +1706,27 @@
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
     </row>
-    <row r="45" spans="1:8">
-      <c r="A45" s="2"/>
-      <c r="B45" s="2" t="s">
+    <row r="45" spans="1:3">
+      <c r="A45" s="2" t="s">
         <v>82</v>
       </c>
+      <c r="B45" s="2"/>
       <c r="C45" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
     </row>
     <row r="46" spans="1:3">
-      <c r="A46" s="2" t="s">
-        <v>84</v>
-      </c>
+      <c r="A46" s="2"/>
       <c r="B46" s="2"/>
-      <c r="C46" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
+      <c r="C46" s="2"/>
+    </row>
+    <row r="47" spans="1:2">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" s="2"/>
-      <c r="B49" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
